--- a/docentes/Flores Ovalle Victor - Estadisticos 20232.xlsx
+++ b/docentes/Flores Ovalle Victor - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="21">
   <si>
     <t>Mat</t>
   </si>
@@ -71,6 +71,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>TENTZOHUA</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>RUBI</t>
   </si>
 </sst>
 </file>
@@ -562,16 +571,19 @@
         <v>29</v>
       </c>
       <c r="D2">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>68.97</v>
+      </c>
+      <c r="H2">
+        <v>5.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -585,16 +597,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>90.63</v>
+      </c>
+      <c r="H3">
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -650,16 +665,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>48.28</v>
+        <v>68.97</v>
       </c>
       <c r="H2">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -676,16 +691,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>87.5</v>
+        <v>90.63</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -695,7 +710,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -725,6 +740,29 @@
         <v>17</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>21330051920107</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Flores Ovalle Victor - Estadisticos 20232.xlsx
+++ b/docentes/Flores Ovalle Victor - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="18">
   <si>
     <t>Mat</t>
   </si>
@@ -71,15 +71,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>TENTZOHUA</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>RUBI</t>
   </si>
 </sst>
 </file>
@@ -665,16 +656,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>68.97</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H2">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -691,16 +682,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>90.63</v>
+        <v>96.88</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -710,7 +701,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -740,29 +731,6 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920107</v>
-      </c>
-      <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Flores Ovalle Victor - Estadisticos 20232.xlsx
+++ b/docentes/Flores Ovalle Victor - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="21">
   <si>
     <t>Mat</t>
   </si>
@@ -71,6 +71,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>GILES</t>
+  </si>
+  <si>
+    <t>FIGUEROA</t>
+  </si>
+  <si>
+    <t>ALEXA YAMILET</t>
   </si>
 </sst>
 </file>
@@ -701,7 +710,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -731,6 +740,29 @@
         <v>17</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>23330051920231</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
